--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,384 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131379115</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>924</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1369_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509411</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6228589</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1369</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131379116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>924</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1368_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509400</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6228584</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1368</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131379119</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>924</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1367_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>509404</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6228581</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1367</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>131379115</v>
       </c>
       <c r="B5" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1227,7 +1227,7 @@
         <v>131379116</v>
       </c>
       <c r="B6" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1353,7 +1353,7 @@
         <v>131379119</v>
       </c>
       <c r="B7" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 27128-2024 artfynd.xlsx
+++ b/artfynd/A 27128-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68016444</v>
+        <v>131379047</v>
       </c>
       <c r="B2" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3374, Bl</t>
+          <t>Hakarp, träd 1480_2022, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509391.9434823333</v>
+        <v>509486</v>
       </c>
       <c r="R2" t="n">
-        <v>6228590.852537207</v>
+        <v>6228606</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>K_Epifyter_22_1480</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,17 +769,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -816,53 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68016443</v>
+        <v>131379074</v>
       </c>
       <c r="B3" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3375, Bl</t>
+          <t>Hakarp, träd 1403_2022, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509409.2158403223</v>
+        <v>509429</v>
       </c>
       <c r="R3" t="n">
-        <v>6228593.115188859</v>
+        <v>6228562</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,27 +866,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>K_Epifyter_22_1403</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -946,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -957,53 +927,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68016445</v>
+        <v>131379090</v>
       </c>
       <c r="B4" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3373, Bl</t>
+          <t>Hakarp, träd 1386_2022, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509396.9961120442</v>
+        <v>509408</v>
       </c>
       <c r="R4" t="n">
-        <v>6228574.178395203</v>
+        <v>6228557</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,27 +992,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>K_Epifyter_22_1386</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1087,7 +1042,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1098,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131379115</v>
+        <v>131379091</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,14 +1084,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1369_2022, Bl</t>
+          <t>Hakarp, träd 1384_2022, Bl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509411</v>
+        <v>509375</v>
       </c>
       <c r="R5" t="n">
-        <v>6228589</v>
+        <v>6228554</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1163,7 +1118,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1369</t>
+          <t>K_Epifyter_22_1384</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1213,7 +1168,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1224,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131379116</v>
+        <v>131379093</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,14 +1210,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1368_2022, Bl</t>
+          <t>Hakarp, träd 1383_2022, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509400</v>
+        <v>509377</v>
       </c>
       <c r="R6" t="n">
-        <v>6228584</v>
+        <v>6228546</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1289,7 +1244,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1368</t>
+          <t>K_Epifyter_22_1383</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1339,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1350,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131379119</v>
+        <v>131379101</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,14 +1336,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1367_2022, Bl</t>
+          <t>Hakarp, träd 1380_2022, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509404</v>
+        <v>509390</v>
       </c>
       <c r="R7" t="n">
-        <v>6228581</v>
+        <v>6228546</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1415,7 +1370,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1367</t>
+          <t>K_Epifyter_22_1380</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1465,10 +1420,2908 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131379102</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>924</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1379_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>509400</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6228551</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1379</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131379105</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>924</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1378_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>509405</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6228551</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1378</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131379106</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>924</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1377_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>509402</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6228557</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1377</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131379109</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>924</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1372_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>509401</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6228565</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1372</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131379111</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>924</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1370_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>509413</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6228574</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1370</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131379113</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>924</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1369_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>509411</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6228589</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1369</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131379116</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>924</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1368_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>509400</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6228584</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1368</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131379119</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>924</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1367_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>509404</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6228581</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1367</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131379120</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>924</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1362_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>509472</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6228573</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1362</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>68016448</v>
+      </c>
+      <c r="B17" t="n">
+        <v>77726</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3370, Bl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>509393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6228564</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>68016433</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3390, Bl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>509376</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6228559</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>68016435</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3390, Bl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>509376</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6228559</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>68016431</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3392, Bl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>509366</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6228565</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3392</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>68016432</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3391, Bl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>509379</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6228552</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>68016434</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3390, Bl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>509376</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6228559</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>68016437</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3385, Bl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>509410</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6228553</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>68016442</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3376, Bl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>509386</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6228555</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>68016443</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3375, Bl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>509409</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6228593</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>68016444</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3374, Bl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>509392</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6228591</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>68016445</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3373, Bl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>509397</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6228574</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>68016446</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3371, Bl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>509396</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6228563</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>68016447</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3370, Bl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>509393</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6228564</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>68016449</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3367, Bl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>509415</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6228571</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
